--- a/data/NAAIM_History.xlsx
+++ b/data/NAAIM_History.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1036"/>
+  <dimension ref="A1:B1041"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,7 +647,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>92.42857142857143</v>
+        <v>92.42857142857144</v>
       </c>
     </row>
     <row r="23">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100.0476190476191</v>
+        <v>100.047619047619</v>
       </c>
     </row>
     <row r="29">
@@ -1347,7 +1347,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>26.68965517241379</v>
+        <v>26.6896551724138</v>
       </c>
     </row>
     <row r="93">
@@ -1377,7 +1377,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>49.86111111111111</v>
+        <v>49.86111111111112</v>
       </c>
     </row>
     <row r="96">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>9.617647058823529</v>
+        <v>9.617647058823527</v>
       </c>
     </row>
     <row r="125">
@@ -1897,7 +1897,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>41.61111111111111</v>
+        <v>41.61111111111112</v>
       </c>
     </row>
     <row r="148">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>59.11111111111111</v>
+        <v>59.11111111111112</v>
       </c>
     </row>
     <row r="216">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>42.3030303030303</v>
+        <v>42.30303030303031</v>
       </c>
     </row>
     <row r="222">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>25.95238095238095</v>
+        <v>25.95238095238096</v>
       </c>
     </row>
     <row r="261">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>20.17073170731707</v>
+        <v>20.17073170731708</v>
       </c>
     </row>
     <row r="271">
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>27.90384615384615</v>
+        <v>27.90384615384616</v>
       </c>
     </row>
     <row r="275">
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>91.06657894736841</v>
+        <v>91.0665789473684</v>
       </c>
     </row>
     <row r="349">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>95.03225806451613</v>
+        <v>95.03225806451611</v>
       </c>
     </row>
     <row r="394">
@@ -4377,7 +4377,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>96.83423076923077</v>
+        <v>96.83423076923076</v>
       </c>
     </row>
     <row r="396">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>95.13384615384615</v>
+        <v>95.13384615384616</v>
       </c>
     </row>
     <row r="397">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>50.86794871794871</v>
+        <v>50.86794871794872</v>
       </c>
     </row>
     <row r="426">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>9.974193548387099</v>
+        <v>9.974193548387101</v>
       </c>
     </row>
     <row r="436">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>92.62228571428571</v>
+        <v>92.62228571428572</v>
       </c>
     </row>
     <row r="451">
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>52.23999999999999</v>
+        <v>52.24</v>
       </c>
     </row>
     <row r="474">
@@ -5707,7 +5707,7 @@
         </is>
       </c>
       <c r="B528" t="n">
-        <v>92.86290322580645</v>
+        <v>92.86290322580643</v>
       </c>
     </row>
     <row r="529">
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="B529" t="n">
-        <v>98.79193548387097</v>
+        <v>98.79193548387096</v>
       </c>
     </row>
     <row r="530">
@@ -5727,7 +5727,7 @@
         </is>
       </c>
       <c r="B530" t="n">
-        <v>97.80000000000001</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="531">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="B551" t="n">
-        <v>94.08620689655173</v>
+        <v>94.08620689655172</v>
       </c>
     </row>
     <row r="552">
@@ -5947,7 +5947,7 @@
         </is>
       </c>
       <c r="B552" t="n">
-        <v>99.28333333333333</v>
+        <v>99.28333333333332</v>
       </c>
     </row>
     <row r="553">
@@ -6097,7 +6097,7 @@
         </is>
       </c>
       <c r="B567" t="n">
-        <v>95.19827586206897</v>
+        <v>95.19827586206895</v>
       </c>
     </row>
     <row r="568">
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="B569" t="n">
-        <v>97.49107142857143</v>
+        <v>97.49107142857144</v>
       </c>
     </row>
     <row r="570">
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="B570" t="n">
-        <v>95.86290322580645</v>
+        <v>95.86290322580643</v>
       </c>
     </row>
     <row r="571">
@@ -6137,7 +6137,7 @@
         </is>
       </c>
       <c r="B571" t="n">
-        <v>92.09821428571429</v>
+        <v>92.09821428571428</v>
       </c>
     </row>
     <row r="572">
@@ -6147,7 +6147,7 @@
         </is>
       </c>
       <c r="B572" t="n">
-        <v>93.37068965517241</v>
+        <v>93.3706896551724</v>
       </c>
     </row>
     <row r="573">
@@ -6177,7 +6177,7 @@
         </is>
       </c>
       <c r="B575" t="n">
-        <v>93.35606060606061</v>
+        <v>93.35606060606059</v>
       </c>
     </row>
     <row r="576">
@@ -6187,7 +6187,7 @@
         </is>
       </c>
       <c r="B576" t="n">
-        <v>90.99038461538461</v>
+        <v>90.9903846153846</v>
       </c>
     </row>
     <row r="577">
@@ -6217,7 +6217,7 @@
         </is>
       </c>
       <c r="B579" t="n">
-        <v>90.94791666666667</v>
+        <v>90.94791666666669</v>
       </c>
     </row>
     <row r="580">
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="B601" t="n">
-        <v>90.39772727272727</v>
+        <v>90.39772727272728</v>
       </c>
     </row>
     <row r="602">
@@ -10788,6 +10788,56 @@
       </c>
       <c r="B1036" t="n">
         <v>96.67</v>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>77.34</v>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>82.02</v>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>98.39</v>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>86.81999999999999</v>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>79.27</v>
       </c>
     </row>
   </sheetData>
